--- a/k_12_forms/027_genetics_and_cell_division_quiz--k_12_forms.xlsx
+++ b/k_12_forms/027_genetics_and_cell_division_quiz--k_12_forms.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,9 +430,9 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +510,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>What is the primary function of the nucleus in a cell?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_1_header</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is Mitosis?</t>
+          <t>What is the process of mitosis?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +556,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What does the word 'mitosis' mean?</t>
+          <t>What is the main difference between mitosis and meiosis?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>section_2_header</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>How does DNA replication occur?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,25 +607,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What is the purpose of meiosis?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>section_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -663,13 +653,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What is the difference between mitosis and meiosis in terms of genetic variation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +676,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What are the stages of meiosis?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +699,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>How does DNA replication affect the cell's genetic information?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +722,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What are the main functions of the cell cycle?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +745,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What is the result of mitosis in terms of genetic variation?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +768,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What are the main differences between mitosis and meiosis in terms of genetic information?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,13 +791,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What is the purpose of DNA replication in the cell cycle?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +814,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>How does meiosis affect genetic variation?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,36 +837,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is Meiosis?</t>
+          <t>What is the role of the cell cycle in cell reproduction?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>section_3_header</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DNA Replication</t>
+          <t>What are the main stages of meiosis?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,13 +883,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What happens during DNA replication?</t>
+          <t>What is the difference between mitosis and meiosis in terms of chromosomal replication?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,43 +906,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is DNA replication?</t>
+          <t>What happens during DNA replication?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>section_4_header</t>
+          <t>question_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quiz Instructions</t>
+          <t>What is the result of mitosis in terms of chromosomal number?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,13 +952,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Please select all that apply</t>
+          <t>What is the expected outcome of this quiz?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -985,13 +975,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is the purpose of this quiz?</t>
+          <t>How will you use this quiz?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1008,13 +998,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How will you be using this quiz?</t>
+          <t>What will you do with the results of this quiz?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1031,13 +1021,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the expected result?</t>
+          <t>What do you expect from this quiz?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1054,13 +1044,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How will you be using this quiz?</t>
+          <t>What questions do you find most challenging?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1077,13 +1067,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the expected result?</t>
+          <t>What do you think about the format of this quiz?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1093,144 +1083,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>list_name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>option_6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Option 6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
